--- a/master-db/chevrolet.xlsx
+++ b/master-db/chevrolet.xlsx
@@ -5,22 +5,22 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kang1\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kang1\Documents\GitHub\ildeung-battery-v1\master-db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EA3CCE4-7633-49D0-957E-A586777F9501}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C1F6D3C-27B5-4C28-9125-0A910DA4CB65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chevrolet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="98">
   <si>
     <t>제조사</t>
   </si>
@@ -320,6 +320,49 @@
   </si>
   <si>
     <t>DF80R</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>임팔라</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>5~20년</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>가솔린</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>임팔라 2.4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>임팔라 3.6</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DIN74L</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>대기</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">AGM80 </t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -682,7 +725,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1531,26 +1574,23 @@
       <c r="A33" t="s">
         <v>8</v>
       </c>
-      <c r="B33" t="s">
-        <v>51</v>
-      </c>
-      <c r="C33" t="s">
-        <v>52</v>
+      <c r="B33" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="E33" t="s">
-        <v>51</v>
+        <v>92</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>94</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="G33" t="s">
-        <v>12</v>
-      </c>
-      <c r="H33" t="s">
-        <v>13</v>
+        <v>95</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1558,22 +1598,19 @@
         <v>8</v>
       </c>
       <c r="B34" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C34" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="E34" t="s">
-        <v>55</v>
+      <c r="E34" s="1" t="s">
+        <v>93</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="G34" t="s">
-        <v>12</v>
+        <v>97</v>
       </c>
       <c r="H34" t="s">
         <v>13</v>
@@ -1587,13 +1624,13 @@
         <v>53</v>
       </c>
       <c r="C35" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>72</v>
       </c>
       <c r="E35" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>75</v>
@@ -1613,13 +1650,13 @@
         <v>53</v>
       </c>
       <c r="C36" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>72</v>
       </c>
       <c r="E36" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>75</v>
@@ -1636,19 +1673,19 @@
         <v>8</v>
       </c>
       <c r="B37" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C37" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="E37" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G37" t="s">
         <v>12</v>
@@ -1668,7 +1705,7 @@
         <v>34</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E38" t="s">
         <v>57</v>
@@ -1688,19 +1725,19 @@
         <v>8</v>
       </c>
       <c r="B39" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C39" t="s">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E39" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="G39" t="s">
         <v>12</v>
@@ -1717,13 +1754,13 @@
         <v>58</v>
       </c>
       <c r="C40" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>78</v>
       </c>
       <c r="E40" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>87</v>
@@ -1743,13 +1780,13 @@
         <v>58</v>
       </c>
       <c r="C41" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>78</v>
       </c>
       <c r="E41" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>87</v>
@@ -1766,19 +1803,19 @@
         <v>8</v>
       </c>
       <c r="B42" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C42" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="E42" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G42" t="s">
         <v>12</v>
@@ -1798,7 +1835,7 @@
         <v>41</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E43" t="s">
         <v>65</v>
@@ -1824,13 +1861,13 @@
         <v>41</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="E44" t="s">
         <v>65</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G44" t="s">
         <v>12</v>
@@ -1844,19 +1881,19 @@
         <v>8</v>
       </c>
       <c r="B45" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C45" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="E45" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G45" t="s">
         <v>12</v>
@@ -1870,16 +1907,16 @@
         <v>8</v>
       </c>
       <c r="B46" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C46" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>72</v>
       </c>
       <c r="E46" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>87</v>
@@ -1888,6 +1925,32 @@
         <v>12</v>
       </c>
       <c r="H46" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" t="s">
+        <v>8</v>
+      </c>
+      <c r="B47" t="s">
+        <v>68</v>
+      </c>
+      <c r="C47" t="s">
+        <v>69</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E47" t="s">
+        <v>68</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G47" t="s">
+        <v>12</v>
+      </c>
+      <c r="H47" t="s">
         <v>13</v>
       </c>
     </row>

--- a/master-db/chevrolet.xlsx
+++ b/master-db/chevrolet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kang1\Documents\GitHub\ildeung-battery-v1\master-db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C1F6D3C-27B5-4C28-9125-0A910DA4CB65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8A69B85-01E6-4BF0-8DE8-B4DE0BF6C44B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -342,18 +342,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>가솔린</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>임팔라 2.4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>임팔라 3.6</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>DIN74L</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -363,6 +351,18 @@
   </si>
   <si>
     <t xml:space="preserve">AGM80 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>가솔린 3.6</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>가솔린 2.4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">임팔라 </t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1581,16 +1581,16 @@
         <v>91</v>
       </c>
       <c r="D33" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F33" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="E33" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>95</v>
-      </c>
       <c r="H33" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1604,13 +1604,13 @@
         <v>52</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="H34" t="s">
         <v>13</v>
